--- a/06 Рынок/Рынок - сводная таблица.xlsx
+++ b/06 Рынок/Рынок - сводная таблица.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\AIoT_Vault_v2\AIoT Vault\06 Рынок\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6EDC6A2115B5C2F211D6C03991D08224C685A625" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB6D186-8385-4AD2-9FF7-C2D5449E84D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Выводы" sheetId="1" r:id="rId1"/>
-    <sheet name="Сводная" sheetId="2" r:id="rId2"/>
-    <sheet name="Требования" sheetId="3" r:id="rId3"/>
+    <sheet name="Сводная" sheetId="2" r:id="rId1"/>
+    <sheet name="Требования" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="161">
   <si>
     <t>№</t>
   </si>
@@ -475,130 +474,46 @@
     <t>NEAR</t>
   </si>
   <si>
-    <t>Рынок Ambient IoT – сводная таблица</t>
-  </si>
-  <si>
-    <t>Цены на октябрь 2026. Источник данных – заметка «Рынок - сводная таблица» в базе AIoT.</t>
-  </si>
-  <si>
-    <t>Устройств в таблице</t>
-  </si>
-  <si>
-    <t>Всего расхождений со стандартом</t>
-  </si>
-  <si>
-    <t>Пунктов, где устройство соответствует стандарту</t>
-  </si>
-  <si>
-    <t>Устройств с чужим протоколом</t>
-  </si>
-  <si>
-    <t>Устройств в нелицензируемом спектре</t>
-  </si>
-  <si>
-    <t>Общие выводы</t>
-  </si>
-  <si>
-    <t>• Три повторяющихся расхождения: нелицензируемый спектр, свой протокол, нет накопителя или есть батарея.</t>
-  </si>
-  <si>
-    <t>• Ни одно устройство не проходит одновременно по спектру (TR 38.769, 6.7.1.1) и процедуре доступа (TR 38.769, 6.3.4).</t>
-  </si>
-  <si>
-    <t>• Считыватели UHF в РФ: стационарные от ~17–27 тыс. ₽, Chainway UR4 от ~47 тыс. ₽ (Клеверенс).</t>
-  </si>
-  <si>
-    <t>Как читать</t>
-  </si>
-  <si>
-    <t>• Лист «Сводная»: одно устройство – несколько строк, по строке на каждое расхождение. Красным – расхождение, зелёным – соответствие, серым – примечание.</t>
-  </si>
-  <si>
-    <t>• Колонки «Пункт» и «Стр. PDF» указывают место в документе; «Стр. PDF» – номер страницы файла, а не номер в колонтитуле.</t>
-  </si>
-  <si>
-    <t>• Лист «Требования»: справочник требований с готовыми Obsidian-ссылками на PDF в базе.</t>
-  </si>
-  <si>
-    <t>• Расхождения «протокол» и «спектр» добавлены для всех устройств, где они следуют из технологии (Gen2, BLE, Wi-Fi, 433/868 МГц), даже если в исходной заметке не были указаны.</t>
-  </si>
-  <si>
     <t>Код</t>
   </si>
   <si>
-    <t>Ссылка в Obsidian (вставить в заметку)</t>
-  </si>
-  <si>
     <t>Ссылка на стандарт (iTecSpec)</t>
   </si>
   <si>
-    <t>Сколько раз встречается</t>
-  </si>
-  <si>
     <t>Нет накопителя</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=52&amp;selection=45,0,50,20|5.1]]</t>
-  </si>
-  <si>
     <t>Дальность ниже цели</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=32&amp;selection=134,0,164,1|4.1]]</t>
-  </si>
-  <si>
     <t>Дальность соответствует цели</t>
   </si>
   <si>
     <t>Чужой протокол</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=160&amp;selection=27,0,31,27|6.3.4]]</t>
-  </si>
-  <si>
     <t>Нелицензируемый спектр</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=186&amp;selection=105,0,105,84|6.7.1.1]]</t>
-  </si>
-  <si>
     <t>Батарея</t>
   </si>
   <si>
-    <t>[[22840-j00.pdf#page=13&amp;selection=242,0,244,11|3.1]]</t>
-  </si>
-  <si>
     <t>Нет усилителя</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=53&amp;selection=29,0,31,33|5.2.1]]</t>
-  </si>
-  <si>
     <t>Только передача</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=55&amp;selection=125,0,127,29|5.2.2.1]]</t>
-  </si>
-  <si>
     <t>Мощность передачи выше нормы</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=60&amp;selection=89,0,91,36|5.2A]]</t>
-  </si>
-  <si>
     <t>Потребление в пределах Device C</t>
   </si>
   <si>
     <t>Потребление между типами</t>
   </si>
   <si>
-    <t>[[38769-k00.pdf#page=52&amp;selection=45,0,50,20|5.1]], [[38769-k00.pdf#page=53&amp;selection=20,0,27,20|5.2]]</t>
-  </si>
-  <si>
     <t>Своя инфраструктура</t>
-  </si>
-  <si>
-    <t>[[38848-i00.pdf#page=10&amp;selection=174,0,178,27|4.2]]</t>
   </si>
   <si>
     <t>Ближняя зона</t>
@@ -608,18 +523,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
       <charset val="1"/>
     </font>
     <font>
@@ -787,72 +696,60 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1119,130 +1016,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="110" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="24.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-    </row>
-    <row r="4" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="6">
-        <f>COUNTA(Сводная!B2:B75)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="6">
-        <f>COUNTIF(Сводная!F2:F75,"расхождение")</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="6">
-        <f>COUNTIF(Сводная!F2:F75,"соответствует")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="6">
-        <f>COUNTIF(Сводная!L2:L75,"PROTO")</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="6">
-        <f>COUNTIF(Сводная!L2:L75,"SPEC")</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-    </row>
-    <row r="10" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-    </row>
-    <row r="15" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L75"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1262,76 +1035,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="21"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
+      <c r="A3" s="14">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="12" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1354,14 +1127,14 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
       <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1384,14 +1157,14 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1414,14 +1187,14 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1444,22 +1217,22 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
+      <c r="A7" s="14">
         <v>2</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1482,14 +1255,14 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1512,14 +1285,14 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
       <c r="E9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1542,22 +1315,22 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="14">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="12" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1580,14 +1353,14 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1610,14 +1383,14 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1640,14 +1413,14 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1670,22 +1443,22 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
+      <c r="A14" s="14">
         <v>4</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="12" t="s">
         <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1708,14 +1481,14 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
       <c r="E15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1738,14 +1511,14 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
       <c r="E16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1768,14 +1541,14 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1788,22 +1561,22 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
+      <c r="A18" s="14">
         <v>5</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1826,14 +1599,14 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1856,14 +1629,14 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1886,14 +1659,14 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -1916,14 +1689,14 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -1936,22 +1709,22 @@
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18">
+      <c r="A23" s="14">
         <v>6</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1974,14 +1747,14 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2004,14 +1777,14 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
       <c r="E25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -2034,14 +1807,14 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
       <c r="E26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -2064,22 +1837,22 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
+      <c r="A27" s="14">
         <v>7</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -2102,14 +1875,14 @@
       </c>
     </row>
     <row r="28" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
       <c r="E28" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -2132,14 +1905,14 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
       <c r="E29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -2162,14 +1935,14 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
       <c r="E30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -2192,14 +1965,14 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
       <c r="E31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -2212,22 +1985,22 @@
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18">
+      <c r="A32" s="14">
         <v>8</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -2250,14 +2023,14 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
       <c r="E33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2280,14 +2053,14 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
       <c r="E34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -2310,14 +2083,14 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -2340,22 +2113,22 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="18">
+      <c r="A36" s="14">
         <v>9</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="9" t="s">
         <v>67</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2378,14 +2151,14 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
       <c r="E37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -2408,14 +2181,14 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
       <c r="E38" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -2438,38 +2211,38 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="21"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="17"/>
       <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="18">
+      <c r="A40" s="14">
         <v>10</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -2492,14 +2265,14 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
       <c r="E41" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -2522,14 +2295,14 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
       <c r="E42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -2552,14 +2325,14 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
       <c r="E43" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -2582,38 +2355,38 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+      <c r="A44" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="21"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="17"/>
       <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="18">
+      <c r="A45" s="14">
         <v>11</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="12" t="s">
         <v>92</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -2636,14 +2409,14 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
       <c r="E46" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -2666,14 +2439,14 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
       <c r="E47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -2696,14 +2469,14 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
       <c r="E48" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F48" s="9" t="s">
+      <c r="F48" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -2726,22 +2499,22 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="18">
+      <c r="A49" s="14">
         <v>12</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="12" t="s">
         <v>106</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -2764,14 +2537,14 @@
       </c>
     </row>
     <row r="50" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
       <c r="E50" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -2794,14 +2567,14 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
       <c r="E51" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -2824,22 +2597,22 @@
       </c>
     </row>
     <row r="52" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="18">
+      <c r="A52" s="14">
         <v>13</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="9" t="s">
         <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -2862,14 +2635,14 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
       <c r="E53" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -2892,14 +2665,14 @@
       </c>
     </row>
     <row r="54" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="15"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
       <c r="E54" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -2922,22 +2695,22 @@
       </c>
     </row>
     <row r="55" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="18">
+      <c r="A55" s="14">
         <v>14</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="12" t="s">
         <v>112</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -2960,14 +2733,14 @@
       </c>
     </row>
     <row r="56" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
       <c r="E56" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -2990,14 +2763,14 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
       <c r="E57" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -3020,22 +2793,22 @@
       </c>
     </row>
     <row r="58" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="18">
+      <c r="A58" s="14">
         <v>15</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="9" t="s">
         <v>77</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -3048,14 +2821,14 @@
       <c r="L58" s="1"/>
     </row>
     <row r="59" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
       <c r="E59" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -3078,14 +2851,14 @@
       </c>
     </row>
     <row r="60" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="15"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
       <c r="E60" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -3108,22 +2881,22 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="18">
+      <c r="A61" s="14">
         <v>16</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C61" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="12" t="s">
         <v>119</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -3146,14 +2919,14 @@
       </c>
     </row>
     <row r="62" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
       <c r="E62" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -3176,14 +2949,14 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
       <c r="E63" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="F63" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -3206,22 +2979,22 @@
       </c>
     </row>
     <row r="64" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
-        <v>17</v>
-      </c>
-      <c r="B64" s="16" t="s">
+      <c r="A64" s="14">
+        <v>17</v>
+      </c>
+      <c r="B64" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -3244,14 +3017,14 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
       <c r="E65" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F65" s="9" t="s">
+      <c r="F65" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -3274,14 +3047,14 @@
       </c>
     </row>
     <row r="66" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
       <c r="E66" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F66" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -3304,14 +3077,14 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
       <c r="E67" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -3334,22 +3107,22 @@
       </c>
     </row>
     <row r="68" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="18">
+      <c r="A68" s="14">
         <v>18</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="9" t="s">
         <v>63</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F68" s="9" t="s">
+      <c r="F68" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -3372,14 +3145,14 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
       <c r="E69" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="F69" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -3402,14 +3175,14 @@
       </c>
     </row>
     <row r="70" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="15"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
       <c r="E70" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="F70" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G70" s="1" t="s">
@@ -3432,22 +3205,22 @@
       </c>
     </row>
     <row r="71" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="18">
-        <v>19</v>
-      </c>
-      <c r="B71" s="16" t="s">
+      <c r="A71" s="14">
+        <v>19</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="9" t="s">
         <v>135</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="7" t="s">
         <v>55</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -3470,14 +3243,14 @@
       </c>
     </row>
     <row r="72" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
       <c r="E72" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -3500,14 +3273,14 @@
       </c>
     </row>
     <row r="73" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
       <c r="E73" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -3530,19 +3303,19 @@
       </c>
     </row>
     <row r="74" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="22" t="s">
+      <c r="A74" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-      <c r="K74" s="21"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="17"/>
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3561,7 +3334,7 @@
       <c r="E75" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="F75" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G75" s="1" t="s">
@@ -3768,9 +3541,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3779,46 +3552,38 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="63.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:7" ht="63.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -3832,23 +3597,16 @@
       <c r="F2" s="3">
         <v>52</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A2)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>24</v>
@@ -3862,23 +3620,16 @@
       <c r="F3" s="3">
         <v>32</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="G3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A3)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>56</v>
@@ -3892,23 +3643,16 @@
       <c r="F4" s="3">
         <v>32</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4" s="12" t="s">
+      <c r="G4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A4)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3922,23 +3666,16 @@
       <c r="F5" s="3">
         <v>160</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H5" s="12" t="s">
+      <c r="G5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A5)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>34</v>
@@ -3952,23 +3689,16 @@
       <c r="F6" s="3">
         <v>186</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H6" s="12" t="s">
+      <c r="G6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A6)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>79</v>
@@ -3982,23 +3712,16 @@
       <c r="F7" s="3">
         <v>13</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H7" s="12" t="s">
+      <c r="G7" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A7)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>85</v>
@@ -4012,23 +3735,16 @@
       <c r="F8" s="3">
         <v>53</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="12" t="s">
+      <c r="G8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A8)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>99</v>
@@ -4042,23 +3758,16 @@
       <c r="F9" s="3">
         <v>55</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" s="12" t="s">
+      <c r="G9" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I9" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A9)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>125</v>
@@ -4072,23 +3781,16 @@
       <c r="F10" s="3">
         <v>60</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H10" s="12" t="s">
+      <c r="G10" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I10" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A10)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>94</v>
@@ -4102,23 +3804,16 @@
       <c r="F11" s="3">
         <v>60</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="12" t="s">
+      <c r="G11" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A11)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="63.2" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" ht="63.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>69</v>
@@ -4132,23 +3827,16 @@
       <c r="F12" s="3">
         <v>52</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" s="12" t="s">
+      <c r="G12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A12)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>133</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>129</v>
@@ -4162,23 +3850,16 @@
       <c r="F13" s="3">
         <v>10</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H13" s="12" t="s">
+      <c r="G13" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I13" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A13)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>145</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>144</v>
@@ -4192,32 +3873,25 @@
       <c r="F14" s="3">
         <v>32</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="12" t="s">
+      <c r="G14" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="I14" s="3">
-        <f>COUNTIF(Сводная!$L$2:$L$75,A14)</f>
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
-    <hyperlink ref="H11" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
-    <hyperlink ref="H12" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
-    <hyperlink ref="H13" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
